--- a/artfynd/A 66350-2021 artfynd.xlsx
+++ b/artfynd/A 66350-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132310057</v>
       </c>
       <c r="B2" t="n">
-        <v>58490</v>
+        <v>58492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 66350-2021 artfynd.xlsx
+++ b/artfynd/A 66350-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132310057</v>
       </c>
       <c r="B2" t="n">
-        <v>58492</v>
+        <v>58493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>132310044</v>
       </c>
       <c r="B3" t="n">
-        <v>57242</v>
+        <v>57243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 66350-2021 artfynd.xlsx
+++ b/artfynd/A 66350-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132310057</v>
       </c>
       <c r="B2" t="n">
-        <v>58493</v>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>132310044</v>
       </c>
       <c r="B3" t="n">
-        <v>57243</v>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 66350-2021 artfynd.xlsx
+++ b/artfynd/A 66350-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132310057</v>
       </c>
       <c r="B2" t="n">
-        <v>58497</v>
+        <v>58498</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>132310044</v>
       </c>
       <c r="B3" t="n">
-        <v>57247</v>
+        <v>57248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 66350-2021 artfynd.xlsx
+++ b/artfynd/A 66350-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132310057</v>
+        <v>132310044</v>
       </c>
       <c r="B2" t="n">
-        <v>58502</v>
+        <v>57269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570805</v>
+        <v>570766</v>
       </c>
       <c r="R2" t="n">
-        <v>6620606</v>
+        <v>6620612</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132310044</v>
+        <v>132310057</v>
       </c>
       <c r="B3" t="n">
-        <v>57252</v>
+        <v>58519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100038</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570766</v>
+        <v>570805</v>
       </c>
       <c r="R3" t="n">
-        <v>6620612</v>
+        <v>6620606</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,6 +902,125 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134320509</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Orrmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>570837</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6620576</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>05:33</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66350-2021 artfynd.xlsx
+++ b/artfynd/A 66350-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132310044</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132310057</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,8 +1036,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134320509</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>